--- a/標案_2026-04-08.xlsx
+++ b/標案_2026-04-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,27 +627,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司</t>
+          <t>台灣電力股份有限公司第二核能發電廠</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1155F025</t>
+          <t>3511509017</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>115年Solaris伺服器維護案(三區)</t>
+          <t>115~117年度核二廠維護管理電腦化系統硬體維護案</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="F7" t="n">
-        <v>798000</v>
+        <v>749700</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -658,27 +658,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司第二核能發電廠</t>
+          <t>台灣電力股份有限公司通霄發電廠</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3511509017</t>
+          <t>3701500031</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>115~117年度核二廠維護管理電腦化系統硬體維護案</t>
+          <t>115年度四用氣體偵測器檢修及維護工作</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46121</v>
+        <v>46127</v>
       </c>
       <c r="F8" t="n">
-        <v>749700</v>
+        <v>894600</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -689,62 +689,62 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司通霄發電廠</t>
+          <t>嘉義市東區嘉北國民小學</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3701500031</t>
+          <t>115010S</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>115年度四用氣體偵測器檢修及維護工作</t>
+          <t>115年度嘉北國小教學區走廊及樓梯間油漆工程委託規畫設計監造案</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="F9" t="n">
-        <v>894600</v>
+        <v>220306</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>油漆</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>嘉義市東區嘉北國民小學</t>
+          <t>嘉義縣太保市公所</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>115010S</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>115年度嘉北國小教學區走廊及樓梯間油漆工程委託規畫設計監造案</t>
+          <t>115年度太保市各里廣播及監視系統新設維護（開口契約）</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>46126</v>
+        <v>46134</v>
       </c>
       <c r="F10" t="n">
-        <v>220306</v>
+        <v>704371</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>油漆</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
@@ -756,22 +756,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>115年度太保市各里廣播及監視系統新設維護（開口契約）</t>
+          <t>115年度太保市水利建造物維護(修)保養勞務作業</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>46120</v>
+        <v>46114</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>46134</v>
+        <v>46121</v>
       </c>
       <c r="F11" t="n">
-        <v>704371</v>
+        <v>382750</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -782,58 +782,58 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>嘉義縣太保市公所</t>
+          <t>嘉義縣消防局</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>115036</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>115年度太保市水利建造物維護(修)保養勞務作業</t>
+          <t>本局廳舍災後復建工程(含局本部、六腳分隊)及第三大隊廳舍與車道修繕補強工程委託規劃設計監造</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>46114</v>
+        <v>46107</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="F12" t="n">
-        <v>382750</v>
+        <v>351225</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>嘉義縣消防局</t>
+          <t>嘉義縣立中埔國民中學</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>115036</t>
+          <t>cpjh115006</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>本局廳舍災後復建工程(含局本部、六腳分隊)及第三大隊廳舍與車道修繕補強工程委託規劃設計監造</t>
+          <t>115年嘉義縣立中埔國民中學東側大門前方低漥地整地及設施修繕工程</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>46122</v>
+        <v>46121</v>
       </c>
       <c r="F13" t="n">
-        <v>351225</v>
+        <v>287205</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -844,58 +844,58 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>嘉義縣立中埔國民中學</t>
+          <t>國立屏東科技大學</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cpjh115006</t>
+          <t>1150326037</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>115年嘉義縣立中埔國民中學東側大門前方低漥地整地及設施修繕工程</t>
+          <t>液相層析串聯質譜儀維護案( LCMSMS6460)</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>46114</v>
+        <v>46111</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>46121</v>
+        <v>46120</v>
       </c>
       <c r="F14" t="n">
-        <v>287205</v>
+        <v>700000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>國立屏東科技大學</t>
+          <t>國立新竹女子高級中學</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1150326037</t>
+          <t>1150402</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>液相層析串聯質譜儀維護案( LCMSMS6460)</t>
+          <t>校園環境及廁所清潔維護採購案</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>46120</v>
+        <v>46128</v>
       </c>
       <c r="F15" t="n">
-        <v>700000</v>
+        <v>900000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -906,58 +906,58 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>國立新竹女子高級中學</t>
+          <t>國立水里高級商工職業學校</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1150402</t>
+          <t>SL1150301</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>校園環境及廁所清潔維護採購案</t>
+          <t>游藝樓屋頂防水修繕工程之委託規劃設計監造技術服務</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>46113</v>
+        <v>46111</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>46128</v>
+        <v>46125</v>
       </c>
       <c r="F16" t="n">
-        <v>900000</v>
+        <v>395600</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>國立水里高級商工職業學校</t>
+          <t>國立澎湖高級海事水產職業學校</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SL1150301</t>
+          <t>PS-2115014</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>游藝樓屋頂防水修繕工程之委託規劃設計監造技術服務</t>
+          <t>「115年度總務處消防設備修繕」財物採購案</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>46111</v>
+        <v>46100</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>46125</v>
+        <v>46120</v>
       </c>
       <c r="F17" t="n">
-        <v>395600</v>
+        <v>297302</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -968,89 +968,89 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>國立澎湖高級海事水產職業學校</t>
+          <t>國立臺北商業大學</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PS-2115014</t>
+          <t>M115-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「115年度總務處消防設備修繕」財物採購案</t>
+          <t>115年臺北校區圖書館牆面粉刷</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>46100</v>
+        <v>46114</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="F18" t="n">
-        <v>297302</v>
+        <v>700833</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>粉刷</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>國立臺北商業大學</t>
+          <t>國立臺北科技大學</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M115-02</t>
+          <t>T1151420055</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>115年臺北校區圖書館牆面粉刷</t>
+          <t xml:space="preserve">外籍生申請系統年度維護暨系統版本更新　</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c r="F19" t="n">
-        <v>700833</v>
+        <v>471041</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>粉刷</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>國立臺北科技大學</t>
+          <t>國立臺南大學</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>T1151420055</t>
+          <t>1151031-TL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">外籍生申請系統年度維護暨系統版本更新　</t>
+          <t>115年度鋼琴維護合約</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>46120</v>
+        <v>46106</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>46125</v>
+        <v>46121</v>
       </c>
       <c r="F20" t="n">
-        <v>471041</v>
+        <v>264400</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1061,89 +1061,89 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>國立臺南大學</t>
+          <t>國立臺灣博物館</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1151031-TL</t>
+          <t>NTM11507b</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>115年度鋼琴維護合約</t>
+          <t>「臺博館南門園區紅樓屋面暨建築外牆修繕規劃設計監造案」</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>46121</v>
+        <v>46120</v>
       </c>
       <c r="F21" t="n">
-        <v>264400</v>
+        <v>975367</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>國立臺灣博物館</t>
+          <t>國立臺灣大學醫學院附設醫院新竹臺大分院</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTM11507b</t>
+          <t>GH151030</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>「臺博館南門園區紅樓屋面暨建築外牆修繕規劃設計監造案」</t>
+          <t>全球資訊網維護</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>46114</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="F22" t="n">
-        <v>975367</v>
+        <v>474000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>國立臺灣大學醫學院附設醫院新竹臺大分院</t>
+          <t>國防部軍醫局</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GH151030</t>
+          <t>NB15080P070</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>全球資訊網維護</t>
+          <t>藥品聯標作業系統建置暨資料庫建構維護及系統支援管理</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
         <v>46114</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="F23" t="n">
-        <v>474000</v>
+        <v>565000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1159,22 +1159,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NB15080P070</t>
+          <t>NE15055P011</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>藥品聯標作業系統建置暨資料庫建構維護及系統支援管理</t>
+          <t>智慧藥櫃保養維護案</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>46114</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>46125</v>
+        <v>46120</v>
       </c>
       <c r="F24" t="n">
-        <v>565000</v>
+        <v>688000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1185,120 +1185,120 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>國防部軍醫局</t>
+          <t>基隆市政府</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NE15055P011</t>
+          <t>KUP115-07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>智慧藥櫃保養維護案</t>
+          <t>115年基隆市公園遊具暨體健設施修繕更新工程委託設計監造技術服務</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>46120</v>
+        <v>46132</v>
       </c>
       <c r="F25" t="n">
-        <v>688000</v>
+        <v>450000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>基隆市政府</t>
+          <t>外交部</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KUP115-07</t>
+          <t>MOFA115039CS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>115年基隆市公園遊具暨體健設施修繕更新工程委託設計監造技術服務</t>
+          <t>外交部樂群樓宿舍4部電梯維護保養委外案</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>46132</v>
+        <v>46126</v>
       </c>
       <c r="F26" t="n">
-        <v>450000</v>
+        <v>576000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>外交部</t>
+          <t>宜蘭縣三星鄉大洲國民小學</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOFA115039CS</t>
+          <t>11504-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>外交部樂群樓宿舍4部電梯維護保養委外案</t>
+          <t>115年度專科教室優化-音樂教室修繕改造財物採購案</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>46126</v>
+        <v>46125</v>
       </c>
       <c r="F27" t="n">
-        <v>576000</v>
+        <v>400000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉大洲國民小學</t>
+          <t>宜蘭縣羅東鎮羅東國民小學</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11504-01</t>
+          <t>LDES-20260319</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>115年度專科教室優化-音樂教室修繕改造財物採購案</t>
+          <t>115年度羅東國小學校教室漏水修繕工程</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>46120</v>
+        <v>46114</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>46125</v>
+        <v>46120</v>
       </c>
       <c r="F28" t="n">
-        <v>400000</v>
+        <v>490652</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1309,27 +1309,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>宜蘭縣羅東鎮羅東國民小學</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LDES-20260319</t>
+          <t>B096-1150402-1B</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>115年度羅東國小學校教室漏水修繕工程</t>
+          <t>屏東縣定古蹟佳冬西隘門白灰牆修繕工程</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c r="F29" t="n">
-        <v>490652</v>
+        <v>537722</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1340,182 +1340,182 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>屏東縣政府警察局</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B096-1150402-1B</t>
+          <t>115-0325</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>屏東縣定古蹟佳冬西隘門白灰牆修繕工程</t>
+          <t>本局「115年度環境清潔維護工作－A案(局本部)及E案(內埔分局)」勞務採購案</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>46120</v>
+        <v>46114</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>46125</v>
+        <v>46121</v>
       </c>
       <c r="F30" t="n">
-        <v>537722</v>
+        <v>950000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>屏東縣政府警察局</t>
+          <t>屏東縣竹田鄉西勢國民小學</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>115-0325</t>
+          <t>SISPS1150401</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>本局「115年度環境清潔維護工作－A案(局本部)及E案(內埔分局)」勞務採購案</t>
+          <t>西棟專科教室大樓修繕工程</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>46121</v>
       </c>
       <c r="F31" t="n">
-        <v>950000</v>
+        <v>990000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>屏東縣竹田鄉西勢國民小學</t>
+          <t>彰化縣和美鎮公所</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SISPS1150401</t>
+          <t>15066B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>西棟專科教室大樓修繕工程</t>
+          <t>115年委辦移動式抽水機維護保養開口契約</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="F32" t="n">
-        <v>990000</v>
+        <v>381000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>彰化縣和美鎮公所</t>
+          <t>彰化縣和美鎮大嘉國民小學</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15066B</t>
+          <t>1150416</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>115年委辦移動式抽水機維護保養開口契約</t>
+          <t>大嘉國小幼兒園遊戲場修繕採購</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>46114</v>
+        <v>46111</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>46122</v>
+        <v>46127</v>
       </c>
       <c r="F33" t="n">
-        <v>381000</v>
+        <v>289000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>彰化縣和美鎮大嘉國民小學</t>
+          <t>彰化縣大城鄉公所</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1150416</t>
+          <t>115016</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>大嘉國小幼兒園遊戲場修繕採購</t>
+          <t>115年度大城鄉大城運動公園植栽綠美化及環境維護（開口契約）</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="F34" t="n">
-        <v>289000</v>
+        <v>900000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>彰化縣大城鄉公所</t>
+          <t>新北市政府交通局</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>115016</t>
+          <t>38229-115-005</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>115年度大城鄉大城運動公園植栽綠美化及環境維護（開口契約）</t>
+          <t>115年度淡水河客船碼頭維護工程委託設計監造技術服務</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>46111</v>
+        <v>46106</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="F35" t="n">
-        <v>900000</v>
+        <v>435946</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1531,22 +1531,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>38229-115-005</t>
+          <t>38229-115-009(更正公告)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>115年度淡水河客船碼頭維護工程委託設計監造技術服務</t>
+          <t>115年度新北市路邊停車標誌標線新設及維護工程委託監造（修正後）</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>46106</v>
+        <v>46120</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c r="F36" t="n">
-        <v>435946</v>
+        <v>881502</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1557,27 +1557,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>新北市政府交通局</t>
+          <t>新北市政府勞工局</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>38229-115-009(更正公告)</t>
+          <t>TPLAB115004</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>115年度新北市路邊停車標誌標線新設及維護工程委託監造（修正後）</t>
+          <t>115年新北市各勞工中心空調設備保養維護委外</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>46125</v>
+        <v>46128</v>
       </c>
       <c r="F37" t="n">
-        <v>881502</v>
+        <v>432000</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1588,27 +1588,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>新北市政府勞工局</t>
+          <t>新北市政府採購處</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TPLAB115004</t>
+          <t>1150331A</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>115年新北市各勞工中心空調設備保養維護委外</t>
+          <t>115年至116年度烏來溫泉公共管線代操作及維護工程設計監造委託技術服務案</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>46128</v>
+        <v>46121</v>
       </c>
       <c r="F38" t="n">
-        <v>432000</v>
+        <v>999459</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1619,27 +1619,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>新北市政府採購處</t>
+          <t>新北市新店區安坑國民小學</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1150331A</t>
+          <t>1150323(更正公告)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>115年至116年度烏來溫泉公共管線代操作及維護工程設計監造委託技術服務案</t>
+          <t>115年新北市社區大學聯合資訊網維護計畫採購</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>46113</v>
+        <v>46111</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>46121</v>
+        <v>46120</v>
       </c>
       <c r="F39" t="n">
-        <v>999459</v>
+        <v>239000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1650,58 +1650,58 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>新北市新店區安坑國民小學</t>
+          <t>新北市林口區南勢國民小學</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1150323(更正公告)</t>
+          <t>nses1150402</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>115年新北市社區大學聯合資訊網維護計畫採購</t>
+          <t>115年風神颱風災損修繕工程</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>46111</v>
+        <v>46114</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="F40" t="n">
-        <v>239000</v>
+        <v>442650</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>新北市林口區南勢國民小學</t>
+          <t>新北市立欽賢國民中學</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nses1150402</t>
+          <t>cejh115-0301</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>115年風神颱風災損修繕工程</t>
+          <t>115年度分部教學大樓一及二樓走廊及天花板修繕工程委託規劃設計監造技術服務</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="F41" t="n">
-        <v>442650</v>
+        <v>187839</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1712,27 +1712,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>新北市立欽賢國民中學</t>
+          <t>新北市立雙溪高級中學</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>cejh115-0301</t>
+          <t>1150326</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>115年度分部教學大樓一及二樓走廊及天花板修繕工程委託規劃設計監造技術服務</t>
+          <t>115年度校園簡易水電修繕開口契約採購案</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>46119</v>
+        <v>46114</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>46125</v>
+        <v>46120</v>
       </c>
       <c r="F42" t="n">
-        <v>187839</v>
+        <v>500000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1743,17 +1743,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>新北市立雙溪高級中學</t>
+          <t>新北市萬里區大鵬國民小學</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1150326</t>
+          <t>DP1150401(更正公告)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>115年度校園簡易水電修繕開口契約採購案</t>
+          <t>地坪安全及校門口修繕</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -1763,7 +1763,7 @@
         <v>46120</v>
       </c>
       <c r="F43" t="n">
-        <v>500000</v>
+        <v>925006</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1774,27 +1774,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>新北市萬里區大鵬國民小學</t>
+          <t>新北市貢寮區和美國民小學</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DP1150401(更正公告)</t>
+          <t>HM11502</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>地坪安全及校門口修繕</t>
+          <t>115年度運動場整建修繕工程-委託設計及監造技術服務</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c r="F44" t="n">
-        <v>925006</v>
+        <v>221018</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1805,17 +1805,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>新北市貢寮區和美國民小學</t>
+          <t>新竹縣政府</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HM11502</t>
+          <t>C115-0024</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>115年度運動場整建修繕工程-委託設計及監造技術服務</t>
+          <t>115、116年「高鐵新竹車站特定區共同管道系統管理維護委託專業服務」監審計畫委託專業服務案</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
@@ -1825,162 +1825,162 @@
         <v>46125</v>
       </c>
       <c r="F45" t="n">
-        <v>221018</v>
+        <v>673000</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>新竹縣政府</t>
+          <t>新竹縣新豐鄉公所</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>C115-0024</t>
+          <t>hfe115_10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>115、116年「高鐵新竹車站特定區共同管道系統管理維護委託專業服務」監審計畫委託專業服務案</t>
+          <t>新豐鄉中正堂屋頂防水修繕工程委託規劃設計及監造服務案</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>46119</v>
+        <v>46106</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>46125</v>
+        <v>46120</v>
       </c>
       <c r="F46" t="n">
-        <v>673000</v>
+        <v>417934</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>新竹縣新豐鄉公所</t>
+          <t>新竹縣湖口鄉公所</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>hfe115_10</t>
+          <t>11503B01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>新豐鄉中正堂屋頂防水修繕工程委託規劃設計及監造服務案</t>
+          <t>115年度湖口鄉步道清整及設施維護工程委託設計監造技術服務案</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>46106</v>
+        <v>46119</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c r="F47" t="n">
-        <v>417934</v>
+        <v>900000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>新竹縣湖口鄉公所</t>
+          <t>新竹縣立成功國民中學</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11503B01</t>
+          <t>CG115040</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>115年度湖口鄉步道清整及設施維護工程委託設計監造技術服務案</t>
+          <t>B棟大樓及B、C棟通廊水泥漆粉刷工程</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="F48" t="n">
-        <v>900000</v>
+        <v>961223</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>粉刷</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>新竹縣立成功國民中學</t>
+          <t>桃園市中壢區大崙國民小學</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CG115040</t>
+          <t>DLES114009</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B棟大樓及B、C棟通廊水泥漆粉刷工程</t>
+          <t>校園戶外設施改善-教材園圍牆修繕工程</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="F49" t="n">
-        <v>961223</v>
+        <v>320000</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>粉刷</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>桃園市中壢區大崙國民小學</t>
+          <t>桃園市中壢區青埔國民小學</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DLES114009</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>校園戶外設施改善-教材園圍牆修繕工程</t>
+          <t>行政大樓四樓平台修繕案</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>46113</v>
+        <v>46108</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>46126</v>
+        <v>46120</v>
       </c>
       <c r="F50" t="n">
-        <v>320000</v>
+        <v>619700</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1991,151 +1991,151 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>桃園市中壢區青埔國民小學</t>
+          <t>桃園市大溪區仁和國民小學</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>行政大樓四樓平台修繕案</t>
+          <t>校舍設備（教室門扇）更新維護採購案</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>46108</v>
+        <v>46120</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="F51" t="n">
-        <v>619700</v>
+        <v>180000</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>桃園市大溪區仁和國民小學</t>
+          <t>桃園市楊梅區瑞塘國民小學</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>C0413-11503</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>校舍設備（教室門扇）更新維護採購案</t>
+          <t>校舍走廊油漆改善工程-委託規劃設計監造技術服務案</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>46120</v>
+        <v>46111</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>46122</v>
+        <v>46120</v>
       </c>
       <c r="F52" t="n">
-        <v>180000</v>
+        <v>182716</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>油漆</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>桃園市楊梅區瑞塘國民小學</t>
+          <t>法務部矯正署屏東監獄</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>C0413-11503</t>
+          <t>pt1150331</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>校舍走廊油漆改善工程-委託規劃設計監造技術服務案</t>
+          <t>115年度場舍修繕材料(水電油漆鐵材泥作)</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>46111</v>
+        <v>46120</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="F53" t="n">
-        <v>182716</v>
+        <v>432275</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>油漆</t>
+          <t>油漆、修繕</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>法務部矯正署屏東監獄</t>
+          <t>海洋委員會海巡署艦隊分署</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>pt1150331</t>
+          <t>B115105</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>115年度場舍修繕材料(水電油漆鐵材泥作)</t>
+          <t>第十六（澳底）海巡隊廳舍結構補強及廳舍修繕工程委託規劃設計及監造技術服務</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>46120</v>
+        <v>46106</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>46126</v>
+        <v>46135</v>
       </c>
       <c r="F54" t="n">
-        <v>432275</v>
+        <v>788827</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>油漆、修繕</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>海洋委員會海巡署艦隊分署</t>
+          <t>澎湖縣政府文化局</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B115105</t>
+          <t>SV-115105</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>第十六（澳底）海巡隊廳舍結構補強及廳舍修繕工程委託規劃設計及監造技術服務</t>
+          <t>澎湖縣歷史建築篤行十村新復路5號因應計畫及修繕工程規劃設計委託技術服務</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>46106</v>
+        <v>46101</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>46135</v>
+        <v>46122</v>
       </c>
       <c r="F55" t="n">
-        <v>788827</v>
+        <v>550000</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2146,58 +2146,58 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>澎湖縣政府文化局</t>
+          <t>經濟部商業發展署</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SV-115105</t>
+          <t>E115015</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>澎湖縣歷史建築篤行十村新復路5號因應計畫及修繕工程規劃設計委託技術服務</t>
+          <t>115年專案計畫管理系統強化暨維護案</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F56" t="n">
-        <v>550000</v>
+        <v>800000</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>經濟部商業發展署</t>
+          <t>經濟部水利署第六河川分署</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>E115015</t>
+          <t>1150501</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>115年專案計畫管理系統強化暨維護案</t>
+          <t>115年度電腦設備維護資訊服務採購案</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>46120</v>
+        <v>46111</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>46125</v>
+        <v>46120</v>
       </c>
       <c r="F57" t="n">
-        <v>800000</v>
+        <v>960564</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2208,27 +2208,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>經濟部水利署第六河川分署</t>
+          <t>考試院</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1150501</t>
+          <t>1152001</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>115年度電腦設備維護資訊服務採購案</t>
+          <t>考試院115年度院區景觀園藝及盆栽租賃委託維護案</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="F58" t="n">
-        <v>960564</v>
+        <v>400000</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2239,27 +2239,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>考試院</t>
+          <t>臺中市政府文化局</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1152001</t>
+          <t>115026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>考試院115年度院區景觀園藝及盆栽租賃委託維護案</t>
+          <t>115年臺中州廳綠美化維護工作委託專業服務案</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>46112</v>
+        <v>46108</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>46121</v>
+        <v>46127</v>
       </c>
       <c r="F59" t="n">
-        <v>400000</v>
+        <v>289275</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2270,58 +2270,58 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>臺中市政府文化局</t>
+          <t>臺中市東勢區公所</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>115026</t>
+          <t>1150309</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>115年臺中州廳綠美化維護工作委託專業服務案</t>
+          <t>東勢區綜合立體停車場地下停車場地坪修繕工程委託設計監造技術服務</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>46127</v>
+        <v>46121</v>
       </c>
       <c r="F60" t="n">
-        <v>289275</v>
+        <v>411692</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>臺中市東勢區公所</t>
+          <t>臺中市豐原區葫蘆墩國民小學</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1150309</t>
+          <t>114hld11</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>東勢區綜合立體停車場地下停車場地坪修繕工程委託設計監造技術服務</t>
+          <t>115年度葫蘆墩國民小學防水、排水及地磚修繕工程</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>46111</v>
+        <v>46120</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>46121</v>
+        <v>46126</v>
       </c>
       <c r="F61" t="n">
-        <v>411692</v>
+        <v>260820</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2332,31 +2332,31 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>臺中市豐原區葫蘆墩國民小學</t>
+          <t>臺北大眾捷運股份有限公司</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>114hld11</t>
+          <t>B15A00386</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>115年度葫蘆墩國民小學防水、排水及地磚修繕工程</t>
+          <t>北投機廠十噸貨梯設備維護工作</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>46126</v>
+        <v>46121</v>
       </c>
       <c r="F62" t="n">
-        <v>260820</v>
+        <v>749745</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
@@ -2368,22 +2368,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B15A00386</t>
+          <t>B15A00387</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>北投機廠十噸貨梯設備維護工作</t>
+          <t>北投機廠及北投旅客服務中心電梯設備維護工作</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>46113</v>
+        <v>46112</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>46121</v>
+        <v>46120</v>
       </c>
       <c r="F63" t="n">
-        <v>749745</v>
+        <v>861000</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2394,27 +2394,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>臺北大眾捷運股份有限公司</t>
+          <t>臺北市停車管理工程處</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B15A00387</t>
+          <t>1153A011</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>北投機廠及北投旅客服務中心電梯設備維護工作</t>
+          <t>115年成德立體停車場機械停車設備等系統維護保養</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>46120</v>
+        <v>46127</v>
       </c>
       <c r="F64" t="n">
-        <v>861000</v>
+        <v>358644</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2425,27 +2425,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>臺北市停車管理工程處</t>
+          <t>臺北市南港區公所</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1153A011</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>115年成德立體停車場機械停車設備等系統維護保養</t>
+          <t>臺北市南港區115年度5-12月各區民活動中心清潔維護案</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="F65" t="n">
-        <v>358644</v>
+        <v>711820</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2456,27 +2456,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>臺北市南港區公所</t>
+          <t>臺北市政府工務局新建工程處</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>臺北市南港區115年度5-12月各區民活動中心清潔維護案</t>
+          <t>115年度容積移轉送出基地屬已開闢未開闢都市計畫道路查詢系統案維護案</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="F66" t="n">
-        <v>711820</v>
+        <v>650000</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2487,27 +2487,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>臺北市政府工務局新建工程處</t>
+          <t>臺北市政府工務局水利工程處</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11502</t>
+          <t>115088</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>115年度容積移轉送出基地屬已開闢未開闢都市計畫道路查詢系統案維護案</t>
+          <t>115年度臺北市積水事件查詢網維護工作</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>46120</v>
+        <v>46106</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>46126</v>
+        <v>46121</v>
       </c>
       <c r="F67" t="n">
-        <v>650000</v>
+        <v>750000</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2518,27 +2518,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>臺北市政府工務局水利工程處</t>
+          <t>臺北市政府環境保護局</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>115088</t>
+          <t>115s047</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>115年度臺北市積水事件查詢網維護工作</t>
+          <t>115年度太陽能臭氧增氧機運轉維護及汛期拆遷採購</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>46106</v>
+        <v>46119</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>46121</v>
+        <v>46126</v>
       </c>
       <c r="F68" t="n">
-        <v>750000</v>
+        <v>264240</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2549,27 +2549,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>臺北市政府環境保護局</t>
+          <t>臺北市政府社會局</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>115s047</t>
+          <t>1152055</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>115年度太陽能臭氧增氧機運轉維護及汛期拆遷採購</t>
+          <t>115年銀髮族方案補助平台擴充及維護委外服務案</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>46126</v>
+        <v>46125</v>
       </c>
       <c r="F69" t="n">
-        <v>264240</v>
+        <v>1000000</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2580,120 +2580,120 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>臺北市政府社會局</t>
+          <t>臺北市政府警察局信義分局</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1152055</t>
+          <t>YU11502</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>115年銀髮族方案補助平台擴充及維護委外服務案</t>
+          <t>115年度分局樓梯地坪整修與牆面油漆粉刷工程技術服務採購案</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="F70" t="n">
-        <v>1000000</v>
+        <v>280000</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>油漆、粉刷</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>臺北市政府警察局信義分局</t>
+          <t>臺北市政府警察局婦幼警察隊</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YU11502</t>
+          <t>115A003(更正公告)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>115年度分局樓梯地坪整修與牆面油漆粉刷工程技術服務採購案</t>
+          <t>婦幼隊外牆飾面修繕工程</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>46119</v>
+        <v>46105</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>46125</v>
+        <v>46120</v>
       </c>
       <c r="F71" t="n">
-        <v>280000</v>
+        <v>932413</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>油漆、粉刷</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>臺北市政府警察局婦幼警察隊</t>
+          <t>臺北市政府資訊局</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>115A003(更正公告)</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>婦幼隊外牆飾面修繕工程</t>
+          <t>事務系統維護服務採購案</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>46105</v>
+        <v>46112</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c r="F72" t="n">
-        <v>932413</v>
+        <v>308000</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>臺北市政府資訊局</t>
+          <t>臺北市立美術館</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>115RE0061</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>事務系統維護服務採購案</t>
+          <t>115年度文獻室數位典藏系統優化暨維護案</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>46125</v>
+        <v>46120</v>
       </c>
       <c r="F73" t="n">
-        <v>308000</v>
+        <v>700000</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2704,27 +2704,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>臺北市立美術館</t>
+          <t>臺北市立陽明教養院</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>115RE0061</t>
+          <t>1150211(更正公告)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>115年度文獻室數位典藏系統優化暨維護案</t>
+          <t>115年度空調設備維護保養採購案</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
         <v>46114</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c r="F74" t="n">
-        <v>700000</v>
+        <v>999734</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2735,27 +2735,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>臺北市立陽明教養院</t>
+          <t>臺北市都市更新處</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1150211(更正公告)</t>
+          <t>115026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>115年度空調設備維護保養採購案</t>
+          <t>115年度興隆整宅環境清潔維護採購案</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="F75" t="n">
-        <v>999734</v>
+        <v>307000</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2766,27 +2766,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>臺北市都市更新處</t>
+          <t>臺北榮民總醫院</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>115026</t>
+          <t>115H001S</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>115年度興隆整宅環境清潔維護採購案</t>
+          <t>醫療影像儲傳系統電腦設備2年維護勞務委外案</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>46120</v>
+        <v>46112</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>46125</v>
+        <v>46122</v>
       </c>
       <c r="F76" t="n">
-        <v>307000</v>
+        <v>929000</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2797,27 +2797,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>臺北榮民總醫院</t>
+          <t>臺南市政府勞工局</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>115H001S</t>
+          <t>115LAB038(更正公告)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>醫療影像儲傳系統電腦設備2年維護勞務委外案</t>
+          <t>臺南市職安健康處115年度勞工申訴案件管理系統維護與功能增修</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F77" t="n">
-        <v>929000</v>
+        <v>639000</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2828,27 +2828,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>臺南市政府勞工局</t>
+          <t>臺南市文化資產管理處</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>115LAB038(更正公告)</t>
+          <t>115TMACH80S</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>臺南市職安健康處115年度勞工申訴案件管理系統維護與功能增修</t>
+          <t>臺南市傳統工藝石磚雕保存者調查研究暨保存維護計畫</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>46111</v>
+        <v>46104</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>46125</v>
+        <v>46120</v>
       </c>
       <c r="F78" t="n">
-        <v>639000</v>
+        <v>1000000</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2859,151 +2859,151 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>臺南市文化資產管理處</t>
+          <t>臺南市東山區東山國民小學</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>115TMACH80S</t>
+          <t>DS1150303</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>臺南市傳統工藝石磚雕保存者調查研究暨保存維護計畫</t>
+          <t>115年度東山國小活動中心舞台修繕工程</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>46104</v>
+        <v>46114</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="F79" t="n">
-        <v>1000000</v>
+        <v>562341</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>臺南市東山區東山國民小學</t>
+          <t>臺南市立南寧高級中學</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DS1150303</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>115年度東山國小活動中心舞台修繕工程</t>
+          <t>115年度南寧高中除草、修樹校園維護勞務案(開口契約)</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>46114</v>
+        <v>46107</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="F80" t="n">
-        <v>562341</v>
+        <v>486000</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>臺南市立南寧高級中學</t>
+          <t>臺東縣臺東市公所</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>1150409</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>115年度南寧高中除草、修樹校園維護勞務案(開口契約)</t>
+          <t>臺東市公所殯葬管理所靈堂(總廳)油漆粉刷勞務採購案</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="E81" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="F81" t="n">
-        <v>486000</v>
+        <v>250000</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>油漆、粉刷</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>臺東縣臺東市公所</t>
+          <t>臺灣嘉義地方法院</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1150409</t>
+          <t>A1150115</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>臺東市公所殯葬管理所靈堂(總廳)油漆粉刷勞務採購案</t>
+          <t>115年辦公大樓空調設備維護保養</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>46113</v>
+        <v>46111</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="F82" t="n">
-        <v>250000</v>
+        <v>686350</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>油漆、粉刷</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>臺灣嘉義地方法院</t>
+          <t>臺灣港務股份有限公司基隆港務分公司</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A1150115</t>
+          <t>A1S260301</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>115年辦公大樓空調設備維護保養</t>
+          <t>115年度臺北港港區防舷材維護勞務工作</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>46111</v>
+        <v>46114</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>46121</v>
+        <v>46120</v>
       </c>
       <c r="F83" t="n">
-        <v>686350</v>
+        <v>848925</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3014,27 +3014,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>臺灣港務股份有限公司基隆港務分公司</t>
+          <t>臺灣臺東地方法院</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>A1S260301</t>
+          <t>1150309</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>115年度臺北港港區防舷材維護勞務工作</t>
+          <t>臺灣臺東地方法院115年(6月至12月) 電腦軟硬體資訊設備維護勞務採購</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
         <v>46114</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c r="F84" t="n">
-        <v>848925</v>
+        <v>736382</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3045,27 +3045,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>臺灣臺東地方法院</t>
+          <t>臺灣高等檢察署</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1150309</t>
+          <t>115-0313YH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>臺灣臺東地方法院115年(6月至12月) 電腦軟硬體資訊設備維護勞務採購</t>
+          <t>115年度六大緝毒系統資料整合平臺維護案</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
         <v>46114</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>46125</v>
+        <v>46121</v>
       </c>
       <c r="F85" t="n">
-        <v>736382</v>
+        <v>600642</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3076,27 +3076,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>臺灣高等檢察署</t>
+          <t>臺灣高等檢察署臺中檢察分署</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>115-0313YH</t>
+          <t>115004</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>115年度六大緝毒系統資料整合平臺維護案</t>
+          <t>115年度臺中司法大廈冷凍空調主機年度保養維護勞務承攬採購案</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
         <v>46114</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>46121</v>
+        <v>46120</v>
       </c>
       <c r="F86" t="n">
-        <v>600642</v>
+        <v>400000</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3107,89 +3107,89 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>臺灣高等檢察署臺中檢察分署</t>
+          <t>臺灣高等法院高雄分院</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>115004</t>
+          <t>1150401</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>115年度臺中司法大廈冷凍空調主機年度保養維護勞務承攬採購案</t>
+          <t>聯合職務宿舍泡沫滅火設備修繕採購案</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
         <v>46114</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>46120</v>
+        <v>46127</v>
       </c>
       <c r="F87" t="n">
-        <v>400000</v>
+        <v>327180</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>臺灣高等法院高雄分院</t>
+          <t>花蓮縣秀林鄉公所</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1150401</t>
+          <t>115CH001</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>聯合職務宿舍泡沫滅火設備修繕採購案</t>
+          <t>115年度本鄉各村擴音廣播設備裝設維護修繕(含遷移)工程採購(開口契約)</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>46114</v>
+        <v>46111</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="F88" t="n">
-        <v>327180</v>
+        <v>443527</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>修繕、維護</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>花蓮縣秀林鄉公所</t>
+          <t>花蓮縣豐濱鄉公所</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>115CH001</t>
+          <t>1150004474</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>115年度本鄉各村擴音廣播設備裝設維護修繕(含遷移)工程採購(開口契約)</t>
+          <t>辦公大樓公有建築修繕維護工程</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>46111</v>
+        <v>46120</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>46128</v>
+        <v>46126</v>
       </c>
       <c r="F89" t="n">
-        <v>443527</v>
+        <v>990716</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3200,89 +3200,89 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>花蓮縣豐濱鄉公所</t>
+          <t>苗栗縣通霄鎮五福國民小學</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1150004474</t>
+          <t>WUFU1150409</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>辦公大樓公有建築修繕維護工程</t>
+          <t>苗栗縣通霄鎮五福國民小學兒童遊戲場設備安全設備修繕及檢驗採購案</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>46126</v>
+        <v>46120</v>
       </c>
       <c r="F90" t="n">
-        <v>990716</v>
+        <v>430000</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>修繕、維護</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>苗栗縣通霄鎮五福國民小學</t>
+          <t>苗栗縣銅鑼鄉公所</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>WUFU1150409</t>
+          <t>115012</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>苗栗縣通霄鎮五福國民小學兒童遊戲場設備安全設備修繕及檢驗採購案</t>
+          <t>115年銅鑼鄉路樹修剪及除草維護開口契約</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="F91" t="n">
-        <v>430000</v>
+        <v>600000</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>苗栗縣銅鑼鄉公所</t>
+          <t>衛生福利部基隆醫院</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>115012</t>
+          <t>V11502</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>115年銅鑼鄉路樹修剪及除草維護開口契約</t>
+          <t>C臂式X光機2台全責性維護保養</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>46126</v>
+        <v>46125</v>
       </c>
       <c r="F92" t="n">
-        <v>600000</v>
+        <v>441000</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3293,17 +3293,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>衛生福利部基隆醫院</t>
+          <t>衛生福利部旗山醫院</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>V11502</t>
+          <t>1150107A</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>C臂式X光機2台全責性維護保養</t>
+          <t>生理監視系統維護案</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
@@ -3313,7 +3313,7 @@
         <v>46125</v>
       </c>
       <c r="F93" t="n">
-        <v>441000</v>
+        <v>579600</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3324,27 +3324,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>衛生福利部旗山醫院</t>
+          <t>農業部林業及自然保育署嘉義分署</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1150107A</t>
+          <t>Ze115-27</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>生理監視系統維護案</t>
+          <t>115年度資訊安全管理制度(ISMS)維護案</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>46120</v>
+        <v>46108</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="F94" t="n">
-        <v>579600</v>
+        <v>673000</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3355,27 +3355,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署嘉義分署</t>
+          <t>農業部桃園區農業改良場</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ze115-27</t>
+          <t>1150303</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>115年度資訊安全管理制度(ISMS)維護案</t>
+          <t>115年田區智慧配水控制系統維護(開口契約)</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>46125</v>
+        <v>46120</v>
       </c>
       <c r="F95" t="n">
-        <v>673000</v>
+        <v>400000</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3386,89 +3386,89 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>農業部桃園區農業改良場</t>
+          <t>農業部農村發展及水土保持署</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1150303</t>
+          <t>1150407020B</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>115年田區智慧配水控制系統維護(開口契約)</t>
+          <t>115年農村水保署防水工程暨廁所修繕工程委託規劃設計監造</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>46106</v>
+        <v>46120</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>46120</v>
+        <v>46132</v>
       </c>
       <c r="F96" t="n">
-        <v>400000</v>
+        <v>330120</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署</t>
+          <t>農業部農業試驗所</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1150407020B</t>
+          <t>1151016</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>115年農村水保署防水工程暨廁所修繕工程委託規劃設計監造</t>
+          <t>115-117電梯保養維護</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>46132</v>
+        <v>46128</v>
       </c>
       <c r="F97" t="n">
-        <v>330120</v>
+        <v>700000</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>農業部農業試驗所</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1151016</t>
+          <t>TT115S14</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>115-117電梯保養維護</t>
+          <t>115A卑南站轄區水門及附屬設施維護(開口契約)</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>46128</v>
+        <v>46120</v>
       </c>
       <c r="F98" t="n">
-        <v>700000</v>
+        <v>600000</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3484,22 +3484,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CN-115-514002-2501-B1U9</t>
+          <t>TY115A006</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>115年度水庫安全維護(東口緊急閘門鋼索更新)工程</t>
+          <t>石頭溪圳幹線等浚渫維護工作</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>46105</v>
+        <v>46112</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="F99" t="n">
-        <v>783300</v>
+        <v>470400</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3515,22 +3515,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TT115S14</t>
+          <t>TY115B008</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>115A卑南站轄區水門及附屬設施維護(開口契約)</t>
+          <t>115年度受益農民大會活動系統維護及資料整理計畫</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="F100" t="n">
-        <v>600000</v>
+        <v>938000</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3541,58 +3541,58 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>雲林縣立雲林國民中學</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TY115A006</t>
+          <t>C1151009</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>石頭溪圳幹線等浚渫維護工作</t>
+          <t>雲林國中教室及走廊線路整線及油漆採購案</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>46112</v>
+        <v>46120</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>46121</v>
+        <v>46126</v>
       </c>
       <c r="F101" t="n">
-        <v>470400</v>
+        <v>700000</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>油漆</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>雲林縣褒忠鄉公所</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TY115B008</t>
+          <t>115-F005-1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>115年度受益農民大會活動系統維護及資料整理計畫</t>
+          <t>褒忠鄉埔姜崙生命紀念園區清潔維護工作案</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>46121</v>
+        <v>46120</v>
       </c>
       <c r="F102" t="n">
-        <v>938000</v>
+        <v>400000</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3603,27 +3603,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>雲林縣立雲林國民中學</t>
+          <t>高雄市三民區鼎金國民小學</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>C1151009</t>
+          <t>djps1150327</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>雲林國中教室及走廊線路整線及油漆採購案</t>
+          <t>115年度忠孝樓信義樓欄杆防鏽油漆工程</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="F103" t="n">
-        <v>700000</v>
+        <v>468000</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3634,27 +3634,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>雲林縣褒忠鄉公所</t>
+          <t>高雄市六龜區公所</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>115-F005-1</t>
+          <t>115F002(更正公告)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>褒忠鄉埔姜崙生命紀念園區清潔維護工作案</t>
+          <t>115年度六龜區中小型移動式抽水機維護保養開口契約</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>46114</v>
+        <v>46107</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="F104" t="n">
-        <v>400000</v>
+        <v>190000</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3665,89 +3665,89 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>高雄市三民區鼎金國民小學</t>
+          <t>高雄市政府衛生局</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>djps1150327</t>
+          <t>115C028</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>115年度忠孝樓信義樓欄杆防鏽油漆工程</t>
+          <t xml:space="preserve"> 115年鹽埕社區心衛中心辦公廳舍環境清潔維護</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>46126</v>
+        <v>46125</v>
       </c>
       <c r="F105" t="n">
-        <v>468000</v>
+        <v>250000</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>油漆</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>高雄市六龜區公所</t>
+          <t>高雄市政府警察局鳳山分局</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>115F002(更正公告)</t>
+          <t>FS115-006</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>115年度六龜區中小型移動式抽水機維護保養開口契約</t>
+          <t>115年鳳山分局鳳崗派出所外牆及頂樓修繕工程勞務部分(規劃設計監造)</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>46126</v>
+        <v>46122</v>
       </c>
       <c r="F106" t="n">
-        <v>190000</v>
+        <v>266000</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>維護</t>
+          <t>修繕</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>高雄市政府衛生局</t>
+          <t>高雄市梓官區公所</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>115C028</t>
+          <t>115019</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 115年鹽埕社區心衛中心辦公廳舍環境清潔維護</t>
+          <t>115年度高雄市梓官區蚵寮公園及頂蚵子寮段15-14地號綠美化維護工作</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="F107" t="n">
-        <v>250000</v>
+        <v>750000</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3758,58 +3758,58 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>高雄市政府警察局鳳山分局</t>
+          <t>高雄市永安區公所</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FS115-006</t>
+          <t>115Y001</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>115年鳳山分局鳳崗派出所外牆及頂樓修繕工程勞務部分(規劃設計監造)</t>
+          <t>115年永安區轄內里廣播系統設施設備維護及整合計畫(開口契約)</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
         <v>46114</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>46122</v>
+        <v>46120</v>
       </c>
       <c r="F108" t="n">
-        <v>266000</v>
+        <v>780000</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>修繕</t>
+          <t>維護</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>高雄市梓官區公所</t>
+          <t>高雄市燕巢區公所</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>115019</t>
+          <t>A1150120</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>115年度高雄市梓官區蚵寮公園及頂蚵子寮段15-14地號綠美化維護工作</t>
+          <t>115年度道路側溝及中小排維護管理工程(開口契約)</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>46119</v>
+        <v>46112</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>46125</v>
+        <v>46121</v>
       </c>
       <c r="F109" t="n">
-        <v>750000</v>
+        <v>742910</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3820,27 +3820,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>高雄市永安區公所</t>
+          <t>高雄市田寮區公所</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>115Y001</t>
+          <t>1151010</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>115年永安區轄內里廣播系統設施設備維護及整合計畫(開口契約)</t>
+          <t>115年度道路側溝、中小排清疏等委託區公所管理維護工程（開口契約）</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>46120</v>
+        <v>46128</v>
       </c>
       <c r="F110" t="n">
-        <v>780000</v>
+        <v>699719</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -3851,27 +3851,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>高雄市燕巢區公所</t>
+          <t>高雄市田寮區公所</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>A1150120</t>
+          <t>1151013</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>115年度道路側溝及中小排維護管理工程(開口契約)</t>
+          <t>115年度田寮區6公尺以下道路維護工程(開口契約)</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>46112</v>
+        <v>46120</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="F111" t="n">
-        <v>742910</v>
+        <v>949200</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -3882,17 +3882,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>高雄市田寮區公所</t>
+          <t>高雄市鼓山區鼓山國民小學</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1151010</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>115年度道路側溝、中小排清疏等委託區公所管理維護工程（開口契約）</t>
+          <t>向陽樓1~4樓排水管修繕工程</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
@@ -3902,71 +3902,9 @@
         <v>46128</v>
       </c>
       <c r="F112" t="n">
-        <v>699719</v>
+        <v>414799</v>
       </c>
       <c r="G112" t="inlineStr">
-        <is>
-          <t>維護</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>高雄市田寮區公所</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>1151013</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>115年度田寮區6公尺以下道路維護工程(開口契約)</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="n">
-        <v>46120</v>
-      </c>
-      <c r="E113" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="F113" t="n">
-        <v>949200</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>維護</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>高雄市鼓山區鼓山國民小學</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>11502</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>向陽樓1~4樓排水管修繕工程</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="n">
-        <v>46120</v>
-      </c>
-      <c r="E114" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="F114" t="n">
-        <v>414799</v>
-      </c>
-      <c r="G114" t="inlineStr">
         <is>
           <t>修繕</t>
         </is>
